--- a/新数据生成/#肉鸽技能选择节奏.xlsx
+++ b/新数据生成/#肉鸽技能选择节奏.xlsx
@@ -449,7 +449,7 @@
     <col width="19.8" customWidth="1" min="3" max="3"/>
     <col width="17.6" customWidth="1" min="4" max="4"/>
     <col width="24.2" customWidth="1" min="5" max="5"/>
-    <col width="26.4" customWidth="1" min="6" max="6"/>
+    <col width="24.2" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="17.6" customWidth="1" min="8" max="8"/>
   </cols>
@@ -482,7 +482,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>获得经验的时间(s)</t>
+          <t>获得经验的时间_s</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>获得经验的时间(s)</t>
+          <t>获得经验的时间_s</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">

--- a/新数据生成/#肉鸽技能选择节奏.xlsx
+++ b/新数据生成/#肉鸽技能选择节奏.xlsx
@@ -2,28 +2,47 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19095" windowHeight="9765" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="肉鸽技能节奏" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -35,7 +54,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,11 +63,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF424242"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00424242"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -59,25 +97,31 @@
     <border/>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="header_default" xfId="1" hidden="0"/>
     <cellStyle name="data_default" xfId="2" hidden="0"/>
   </cellStyles>
@@ -442,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -452,881 +496,1259 @@
     <col width="24.2" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="17.6" customWidth="1" min="8" max="8"/>
+    <col width="17.6" customWidth="1" min="9" max="9"/>
+    <col width="17.6" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>肉鸽技能升级次数</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>理论所需经验值</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>玩家消除行数</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>玩家获得的经验总值</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>获得经验的时间_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>时间取整每30s</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>根据时间计数</t>
         </is>
       </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>怪物波次模拟</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>选择技能次数</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>总次数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>肉鸽技能升级次数</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>理论所需经验值</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>玩家消除行数</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>玩家获得的经验总值</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>获得经验的时间_s</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>时间取整每30s</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>根据时间计数</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>怪物波次模拟</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>选择技能次数</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>总次数</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="4" t="n">
         <v>280</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>18.8</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="4">
         <f>ROUNDUP(F4/30,0)</f>
         <v/>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="4">
         <f>COUNTIF($G$4:$G4,$G4)</f>
         <v/>
       </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I4),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="4">
+        <f>SUM($J$4:$J4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="4" t="n">
         <v>288.5</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>37.5</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="4">
         <f>ROUNDUP(F5/30,0)</f>
         <v/>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="4">
         <f>COUNTIF($G$4:$G5,$G5)</f>
         <v/>
       </c>
+      <c r="I5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I5),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>SUM($J$4:$J5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="4" t="n">
         <v>297.5</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>56.2</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="4">
         <f>ROUNDUP(F6/30,0)</f>
         <v/>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="4">
         <f>COUNTIF($G$4:$G6,$G6)</f>
         <v/>
       </c>
+      <c r="I6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I6),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="4">
+        <f>SUM($J$4:$J6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="4" t="n">
         <v>307</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>1300</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>81.2</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="4">
         <f>ROUNDUP(F7/30,0)</f>
         <v/>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="4">
         <f>COUNTIF($G$4:$G7,$G7)</f>
         <v/>
       </c>
+      <c r="I7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I7),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="4">
+        <f>SUM($J$4:$J7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="4" t="n">
         <v>317</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>1700</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>106.2</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="4">
         <f>ROUNDUP(F8/30,0)</f>
         <v/>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="4">
         <f>COUNTIF($G$4:$G8,$G8)</f>
         <v/>
       </c>
+      <c r="I8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I8),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="4">
+        <f>SUM($J$4:$J8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="4" t="n">
         <v>327.5</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>2100</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>131.2</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="4">
         <f>ROUNDUP(F9/30,0)</f>
         <v/>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="4">
         <f>COUNTIF($G$4:$G9,$G9)</f>
         <v/>
       </c>
+      <c r="I9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I9),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="4">
+        <f>SUM($J$4:$J9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="4" t="n">
         <v>338.5</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="4" t="n">
         <v>2500</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="4" t="n">
         <v>156.2</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="4">
         <f>ROUNDUP(F10/30,0)</f>
         <v/>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="4">
         <f>COUNTIF($G$4:$G10,$G10)</f>
         <v/>
       </c>
+      <c r="I10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I10),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="4">
+        <f>SUM($J$4:$J10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="4" t="n">
         <v>2900</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="4" t="n">
         <v>181.2</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="4">
         <f>ROUNDUP(F11/30,0)</f>
         <v/>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="4">
         <f>COUNTIF($G$4:$G11,$G11)</f>
         <v/>
       </c>
+      <c r="I11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I11),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="4">
+        <f>SUM($J$4:$J11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="4" t="n">
         <v>362</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="4" t="n">
         <v>3300</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="4" t="n">
         <v>206.2</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="4">
         <f>ROUNDUP(F12/30,0)</f>
         <v/>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="4">
         <f>COUNTIF($G$4:$G12,$G12)</f>
         <v/>
       </c>
+      <c r="I12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I12),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="4">
+        <f>SUM($J$4:$J12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="4" t="n">
         <v>374.5</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="4" t="n">
         <v>3700</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="4" t="n">
         <v>231.2</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="4">
         <f>ROUNDUP(F13/30,0)</f>
         <v/>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="4">
         <f>COUNTIF($G$4:$G13,$G13)</f>
         <v/>
       </c>
+      <c r="I13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I13),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="4">
+        <f>SUM($J$4:$J13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="4" t="n">
         <v>387.5</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="4" t="n">
         <v>4100</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="4" t="n">
         <v>256.2</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="4">
         <f>ROUNDUP(F14/30,0)</f>
         <v/>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="4">
         <f>COUNTIF($G$4:$G14,$G14)</f>
         <v/>
       </c>
+      <c r="I14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J14" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I14),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="4">
+        <f>SUM($J$4:$J14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="4" t="n">
         <v>401</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="4" t="n">
         <v>4600</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="4" t="n">
         <v>287.5</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="4">
         <f>ROUNDUP(F15/30,0)</f>
         <v/>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="4">
         <f>COUNTIF($G$4:$G15,$G15)</f>
         <v/>
       </c>
+      <c r="I15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I15),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="4">
+        <f>SUM($J$4:$J15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="4" t="n">
         <v>415</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="4" t="n">
         <v>5100</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="4" t="n">
         <v>318.8</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="4">
         <f>ROUNDUP(F16/30,0)</f>
         <v/>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="4">
         <f>COUNTIF($G$4:$G16,$G16)</f>
         <v/>
       </c>
+      <c r="I16" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J16" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I16),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="4">
+        <f>SUM($J$4:$J16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="4" t="n">
         <v>429.5</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="4" t="n">
         <v>5600</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="4">
         <f>ROUNDUP(F17/30,0)</f>
         <v/>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="4">
         <f>COUNTIF($G$4:$G17,$G17)</f>
         <v/>
       </c>
+      <c r="I17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J17" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I17),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="4">
+        <f>SUM($J$4:$J17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="4" t="n">
         <v>444.5</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="4" t="n">
         <v>6100</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="4" t="n">
         <v>381.2</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="4">
         <f>ROUNDUP(F18/30,0)</f>
         <v/>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="4">
         <f>COUNTIF($G$4:$G18,$G18)</f>
         <v/>
       </c>
+      <c r="I18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I18),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="4">
+        <f>SUM($J$4:$J18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="4" t="n">
         <v>460</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="4" t="n">
         <v>6600</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="4" t="n">
         <v>412.5</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="4">
         <f>ROUNDUP(F19/30,0)</f>
         <v/>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="4">
         <f>COUNTIF($G$4:$G19,$G19)</f>
         <v/>
       </c>
+      <c r="I19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J19" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I19),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="4">
+        <f>SUM($J$4:$J19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="4" t="n">
         <v>476</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="4" t="n">
         <v>7100</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="4" t="n">
         <v>443.8</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="4">
         <f>ROUNDUP(F20/30,0)</f>
         <v/>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="4">
         <f>COUNTIF($G$4:$G20,$G20)</f>
         <v/>
       </c>
+      <c r="I20" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J20" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I20),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="4">
+        <f>SUM($J$4:$J20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="4" t="n">
         <v>492.5</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="4" t="n">
         <v>7600</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="4" t="n">
         <v>475</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="4">
         <f>ROUNDUP(F21/30,0)</f>
         <v/>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="4">
         <f>COUNTIF($G$4:$G21,$G21)</f>
         <v/>
       </c>
+      <c r="I21" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J21" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I21),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="4">
+        <f>SUM($J$4:$J21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="4" t="n">
         <v>509.5</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="4" t="n">
         <v>8200</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="4" t="n">
         <v>512.5</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="4">
         <f>ROUNDUP(F22/30,0)</f>
         <v/>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="4">
         <f>COUNTIF($G$4:$G22,$G22)</f>
         <v/>
       </c>
+      <c r="I22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J22" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I22),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="4">
+        <f>SUM($J$4:$J22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="4" t="n">
         <v>527</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="4" t="n">
         <v>8800</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="4" t="n">
         <v>550</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="4">
         <f>ROUNDUP(F23/30,0)</f>
         <v/>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="4">
         <f>COUNTIF($G$4:$G23,$G23)</f>
         <v/>
       </c>
+      <c r="I23" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I23),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="4">
+        <f>SUM($J$4:$J23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="4" t="n">
         <v>545</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="4" t="n">
         <v>9400</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="4" t="n">
         <v>587.5</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="4">
         <f>ROUNDUP(F24/30,0)</f>
         <v/>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="4">
         <f>COUNTIF($G$4:$G24,$G24)</f>
         <v/>
       </c>
+      <c r="I24" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J24" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I24),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="4">
+        <f>SUM($J$4:$J24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="4" t="n">
         <v>563.5</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="4" t="n">
         <v>625</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="4">
         <f>ROUNDUP(F25/30,0)</f>
         <v/>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="4">
         <f>COUNTIF($G$4:$G25,$G25)</f>
         <v/>
       </c>
+      <c r="I25" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J25" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I25),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="4">
+        <f>SUM($J$4:$J25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="4" t="n">
         <v>582.5</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="4" t="n">
         <v>10600</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="4" t="n">
         <v>662.5</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="4">
         <f>ROUNDUP(F26/30,0)</f>
         <v/>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="4">
         <f>COUNTIF($G$4:$G26,$G26)</f>
         <v/>
       </c>
+      <c r="I26" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J26" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I26),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="4">
+        <f>SUM($J$4:$J26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="2" t="n">
+      <c r="B27" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="4" t="n">
         <v>602</v>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="4" t="n">
         <v>11300</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="4" t="n">
         <v>706.2</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="4">
         <f>ROUNDUP(F27/30,0)</f>
         <v/>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="4">
         <f>COUNTIF($G$4:$G27,$G27)</f>
         <v/>
       </c>
+      <c r="I27" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J27" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I27),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="4">
+        <f>SUM($J$4:$J27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="4" t="n">
         <v>622</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="4" t="n">
         <v>12000</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="4">
         <f>ROUNDUP(F28/30,0)</f>
         <v/>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="4">
         <f>COUNTIF($G$4:$G28,$G28)</f>
         <v/>
       </c>
+      <c r="I28" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J28" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I28),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="4">
+        <f>SUM($J$4:$J28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="4" t="n">
         <v>622</v>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="4" t="n">
         <v>12700</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="4" t="n">
         <v>793.8</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="4">
         <f>ROUNDUP(F29/30,0)</f>
         <v/>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="4">
         <f>COUNTIF($G$4:$G29,$G29)</f>
         <v/>
       </c>
+      <c r="I29" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J29" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I29),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="4">
+        <f>SUM($J$4:$J29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="4" t="n">
         <v>622</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="4" t="n">
         <v>13400</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="4" t="n">
         <v>837.5</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="4">
         <f>ROUNDUP(F30/30,0)</f>
         <v/>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="4">
         <f>COUNTIF($G$4:$G30,$G30)</f>
         <v/>
       </c>
+      <c r="I30" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J30" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I30),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="4">
+        <f>SUM($J$4:$J30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="4" t="n">
         <v>622</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="4" t="n">
         <v>14100</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="4" t="n">
         <v>881.2</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="4">
         <f>ROUNDUP(F31/30,0)</f>
         <v/>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="4">
         <f>COUNTIF($G$4:$G31,$G31)</f>
         <v/>
       </c>
+      <c r="I31" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J31" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I31),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="4">
+        <f>SUM($J$4:$J31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="4" t="n">
         <v>622</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="4" t="n">
         <v>14800</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="4" t="n">
         <v>925</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" s="4">
         <f>ROUNDUP(F32/30,0)</f>
         <v/>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="4">
         <f>COUNTIF($G$4:$G32,$G32)</f>
         <v/>
       </c>
+      <c r="I32" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J32" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I32),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K32" s="4">
+        <f>SUM($J$4:$J32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" s="4" t="n">
         <v>622</v>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="4" t="n">
         <v>15500</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" s="4" t="n">
         <v>968.8</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" s="4">
         <f>ROUNDUP(F33/30,0)</f>
         <v/>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="4">
         <f>COUNTIF($G$4:$G33,$G33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" s="4">
+        <f>IFERROR(LOOKUP(2,1/($G$4:$G500 = I33),$H$4:$H500),0)</f>
+        <v/>
+      </c>
+      <c r="K33" s="4">
+        <f>SUM($J$4:$J33)</f>
         <v/>
       </c>
     </row>
